--- a/results/excel_reports/sipakmed_cropped_efficientnet.pth_llama3.2-vision-binary_blur.xlsx
+++ b/results/excel_reports/sipakmed_cropped_efficientnet.pth_llama3.2-vision-binary_blur.xlsx
@@ -719,110 +719,122 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8115763546798029</v>
+        <v>0.8140394088669951</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8103448275862069</v>
+        <v>0.8165024630541872</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7967980295566502</v>
+        <v>0.812807881773399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7980295566502463</v>
+        <v>0.8017241379310345</v>
       </c>
       <c r="F2" t="n">
-        <v>0.791871921182266</v>
+        <v>0.7795566502463054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>0.7881773399014779</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7746305418719212</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7783251231527094</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7746305418719212</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7561576354679803</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7561576354679803</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.7389162561576355</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7327586206896551</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7229064039408867</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7192118226600985</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.7056650246305419</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.6748768472906403</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6366995073891626</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5812807881773399</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8140394088669951</v>
+        <v>0.8115763546798029</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8165024630541872</v>
+        <v>0.8103448275862069</v>
       </c>
       <c r="D3" t="n">
-        <v>0.812807881773399</v>
+        <v>0.7967980295566502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8017241379310345</v>
+        <v>0.7980295566502463</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7795566502463054</v>
+        <v>0.791871921182266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7881773399014779</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.7746305418719212</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7783251231527094</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7746305418719212</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7561576354679803</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.7561576354679803</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7389162561576355</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.7327586206896551</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.7229064039408867</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.7192118226600985</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.7056650246305419</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.6785714285714286</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.6748768472906403</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.6366995073891626</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.5812807881773399</v>
-      </c>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:U3">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
